--- a/data/f1_fantasy_archive.xlsx
+++ b/data/f1_fantasy_archive.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98229F0-2B07-4F07-A68F-AC4F3D4F854E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="13" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
+    <workbookView activeTab="15" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Drivers Points" sheetId="1" r:id="rId1"/>
@@ -5811,6 +5811,9 @@
       <c r="P1" s="3">
         <v>14</v>
       </c>
+      <c r="Q1" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -5859,6 +5862,9 @@
         <v>32</v>
       </c>
       <c r="P2" s="2">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5909,6 +5915,9 @@
         <v>35</v>
       </c>
       <c r="P3" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5959,6 +5968,9 @@
         <v>33</v>
       </c>
       <c r="P4" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6009,6 +6021,9 @@
         <v>93</v>
       </c>
       <c r="P5" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6059,6 +6074,9 @@
         <v>37</v>
       </c>
       <c r="P6" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6105,6 +6123,9 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
@@ -6153,6 +6174,9 @@
         <v>26</v>
       </c>
       <c r="P8" s="2">
+        <v>-13</v>
+      </c>
+      <c r="Q8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6203,6 +6227,9 @@
         <v>-12</v>
       </c>
       <c r="P9" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6253,6 +6280,9 @@
         <v>17</v>
       </c>
       <c r="P10" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6303,6 +6333,9 @@
         <v>14</v>
       </c>
       <c r="P11" s="2">
+        <v>-18</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6349,6 +6382,9 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
@@ -6397,6 +6433,9 @@
         <v>11</v>
       </c>
       <c r="P13" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6447,6 +6486,9 @@
         <v>-10</v>
       </c>
       <c r="P14" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6497,6 +6539,9 @@
         <v>-10</v>
       </c>
       <c r="P15" s="2">
+        <v>-22</v>
+      </c>
+      <c r="Q15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6547,6 +6592,9 @@
         <v>10</v>
       </c>
       <c r="P16" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6597,6 +6645,9 @@
         <v>4</v>
       </c>
       <c r="P17" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6647,6 +6698,9 @@
         <v>14</v>
       </c>
       <c r="P18" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6699,6 +6753,9 @@
       <c r="P19" s="2">
         <v>0</v>
       </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
@@ -6747,6 +6804,9 @@
         <v>14</v>
       </c>
       <c r="P20" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6797,6 +6857,9 @@
         <v>14</v>
       </c>
       <c r="P21" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6847,6 +6910,9 @@
         <v>4</v>
       </c>
       <c r="P22" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6897,6 +6963,9 @@
         <v>13</v>
       </c>
       <c r="P23" s="2">
+        <v>-18</v>
+      </c>
+      <c r="Q23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6915,8 +6984,9 @@
         <v>25</v>
       </c>
       <c r="P24" s="2">
-        <v>0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
@@ -6932,8 +7002,9 @@
         <v>17</v>
       </c>
       <c r="P25" s="2">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6991,6 +7062,9 @@
         <v>13</v>
       </c>
       <c r="O1" s="3">
+        <v>15</v>
+      </c>
+      <c r="P1" s="3">
         <v>14</v>
       </c>
     </row>
@@ -7038,6 +7112,9 @@
         <v>77</v>
       </c>
       <c r="O2" s="2">
+        <v>44</v>
+      </c>
+      <c r="P2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7085,6 +7162,9 @@
         <v>24</v>
       </c>
       <c r="O3" s="2">
+        <v>18</v>
+      </c>
+      <c r="P3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7132,6 +7212,9 @@
         <v>69</v>
       </c>
       <c r="O4" s="2">
+        <v>59</v>
+      </c>
+      <c r="P4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7179,6 +7262,9 @@
         <v>128</v>
       </c>
       <c r="O5" s="2">
+        <v>87</v>
+      </c>
+      <c r="P5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7226,6 +7312,9 @@
         <v>34</v>
       </c>
       <c r="O6" s="2">
+        <v>-11</v>
+      </c>
+      <c r="P6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7273,6 +7362,9 @@
         <v>17</v>
       </c>
       <c r="O7" s="2">
+        <v>11</v>
+      </c>
+      <c r="P7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7320,6 +7412,9 @@
         <v>33</v>
       </c>
       <c r="O8" s="2">
+        <v>13</v>
+      </c>
+      <c r="P8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7367,6 +7462,9 @@
         <v>41</v>
       </c>
       <c r="O9" s="2">
+        <v>10</v>
+      </c>
+      <c r="P9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7414,6 +7512,9 @@
         <v>-21</v>
       </c>
       <c r="O10" s="2">
+        <v>-17</v>
+      </c>
+      <c r="P10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7461,6 +7562,9 @@
         <v>38</v>
       </c>
       <c r="O11" s="2">
+        <v>24</v>
+      </c>
+      <c r="P11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7508,6 +7612,9 @@
         <v>16</v>
       </c>
       <c r="O12" s="2">
+        <v>-16</v>
+      </c>
+      <c r="P12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7572,6 +7679,9 @@
       <c r="P1" s="3">
         <v>14</v>
       </c>
+      <c r="Q1" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -7622,6 +7732,9 @@
       <c r="P2" s="1">
         <v>26.7</v>
       </c>
+      <c r="Q2" s="1">
+        <v>27</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -7672,6 +7785,9 @@
       <c r="P3" s="1">
         <v>24</v>
       </c>
+      <c r="Q3" s="1">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
@@ -7722,6 +7838,9 @@
       <c r="P4" s="1">
         <v>27.7</v>
       </c>
+      <c r="Q4" s="1">
+        <v>27.8</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -7772,6 +7891,9 @@
       <c r="P5" s="1">
         <v>26.3</v>
       </c>
+      <c r="Q5" s="1">
+        <v>26.6</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
@@ -7822,6 +7944,9 @@
       <c r="P6" s="1">
         <v>27.4</v>
       </c>
+      <c r="Q6" s="1">
+        <v>27.3</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
@@ -7864,6 +7989,9 @@
         <v>13.9</v>
       </c>
       <c r="N7" s="1"/>
+      <c r="Q7" s="1">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
@@ -7914,6 +8042,9 @@
       <c r="P8" s="1">
         <v>25.2</v>
       </c>
+      <c r="Q8" s="1">
+        <v>24.9</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -7964,6 +8095,9 @@
       <c r="P9" s="1">
         <v>24.1</v>
       </c>
+      <c r="Q9" s="1">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
@@ -8014,6 +8148,9 @@
       <c r="P10" s="1">
         <v>5.8</v>
       </c>
+      <c r="Q10" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
@@ -8064,6 +8201,9 @@
       <c r="P11" s="1">
         <v>9.6</v>
       </c>
+      <c r="Q11" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -8106,6 +8246,9 @@
         <v>9.7</v>
       </c>
       <c r="N12" s="1"/>
+      <c r="Q12" s="1">
+        <v>9.7</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
@@ -8156,6 +8299,9 @@
       <c r="P13" s="1">
         <v>8</v>
       </c>
+      <c r="Q13" s="1">
+        <v>8.2</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
@@ -8206,6 +8352,9 @@
       <c r="P14" s="1">
         <v>7</v>
       </c>
+      <c r="Q14" s="1">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
@@ -8256,6 +8405,9 @@
       <c r="P15" s="1">
         <v>3</v>
       </c>
+      <c r="Q15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
@@ -8306,6 +8458,9 @@
       <c r="P16" s="1">
         <v>9.5</v>
       </c>
+      <c r="Q16" s="1">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
@@ -8356,6 +8511,9 @@
       <c r="P17" s="1">
         <v>6.4</v>
       </c>
+      <c r="Q17" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
@@ -8406,6 +8564,9 @@
       <c r="P18" s="1">
         <v>4.2</v>
       </c>
+      <c r="Q18" s="1">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
@@ -8456,6 +8617,9 @@
       <c r="P19" s="1">
         <v>8.6</v>
       </c>
+      <c r="Q19" s="1">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
@@ -8506,6 +8670,9 @@
       <c r="P20" s="1">
         <v>12.2</v>
       </c>
+      <c r="Q20" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
@@ -8556,6 +8723,9 @@
       <c r="P21" s="1">
         <v>10.4</v>
       </c>
+      <c r="Q21" s="1">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
@@ -8606,6 +8776,9 @@
       <c r="P22" s="1">
         <v>3</v>
       </c>
+      <c r="Q22" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
@@ -8654,6 +8827,9 @@
         <v>3.2</v>
       </c>
       <c r="P23" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="1">
         <v>3</v>
       </c>
     </row>
@@ -8750,6 +8926,9 @@
       <c r="O1" s="3">
         <v>14</v>
       </c>
+      <c r="P1" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -8797,6 +8976,9 @@
       <c r="O2" s="1">
         <v>31.6</v>
       </c>
+      <c r="P2" s="1">
+        <v>31.9</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
@@ -8844,6 +9026,9 @@
       <c r="O3" s="1">
         <v>27.2</v>
       </c>
+      <c r="P3" s="1">
+        <v>27.5</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
@@ -8891,6 +9076,9 @@
       <c r="O4" s="1">
         <v>31.5</v>
       </c>
+      <c r="P4" s="1">
+        <v>31.8</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -8938,6 +9126,9 @@
       <c r="O5" s="1">
         <v>33.2</v>
       </c>
+      <c r="P5" s="1">
+        <v>33.5</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
@@ -8985,6 +9176,9 @@
       <c r="O6" s="1">
         <v>13.8</v>
       </c>
+      <c r="P6" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
@@ -9032,6 +9226,9 @@
       <c r="O7" s="1">
         <v>14.1</v>
       </c>
+      <c r="P7" s="1">
+        <v>14.7</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
@@ -9079,6 +9276,9 @@
       <c r="O8" s="1">
         <v>10.8</v>
       </c>
+      <c r="P8" s="1">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
@@ -9126,6 +9326,9 @@
       <c r="O9" s="1">
         <v>6.9</v>
       </c>
+      <c r="P9" s="1">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
@@ -9173,6 +9376,9 @@
       <c r="O10" s="1">
         <v>19.2</v>
       </c>
+      <c r="P10" s="1">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
@@ -9220,6 +9426,9 @@
       <c r="O11" s="1">
         <v>8</v>
       </c>
+      <c r="P11" s="1">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
@@ -9265,6 +9474,9 @@
         <v>3</v>
       </c>
       <c r="O12" s="1">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1">
         <v>3</v>
       </c>
     </row>

--- a/data/f1_fantasy_archive.xlsx
+++ b/data/f1_fantasy_archive.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98229F0-2B07-4F07-A68F-AC4F3D4F854E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="15" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
+    <workbookView activeTab="13" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Drivers Points" sheetId="1" r:id="rId1"/>
@@ -5814,6 +5814,9 @@
       <c r="Q1" s="3">
         <v>15</v>
       </c>
+      <c r="R1" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -5865,6 +5868,9 @@
         <v>23</v>
       </c>
       <c r="Q2" s="2">
+        <v>-11</v>
+      </c>
+      <c r="R2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5920,6 +5926,9 @@
       <c r="Q3" s="2">
         <v>0</v>
       </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
@@ -5971,6 +5980,9 @@
         <v>27</v>
       </c>
       <c r="Q4" s="2">
+        <v>45</v>
+      </c>
+      <c r="R4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6024,6 +6036,9 @@
         <v>35</v>
       </c>
       <c r="Q5" s="2">
+        <v>28</v>
+      </c>
+      <c r="R5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6077,6 +6092,9 @@
         <v>38</v>
       </c>
       <c r="Q6" s="2">
+        <v>43</v>
+      </c>
+      <c r="R6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6124,6 +6142,9 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2">
+        <v>26</v>
+      </c>
+      <c r="R7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6177,6 +6198,9 @@
         <v>-13</v>
       </c>
       <c r="Q8" s="2">
+        <v>15</v>
+      </c>
+      <c r="R8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6230,6 +6254,9 @@
         <v>19</v>
       </c>
       <c r="Q9" s="2">
+        <v>20</v>
+      </c>
+      <c r="R9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6283,6 +6310,9 @@
         <v>4</v>
       </c>
       <c r="Q10" s="2">
+        <v>-16</v>
+      </c>
+      <c r="R10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6336,6 +6366,9 @@
         <v>-18</v>
       </c>
       <c r="Q11" s="2">
+        <v>15</v>
+      </c>
+      <c r="R11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6383,6 +6416,9 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2">
+        <v>3</v>
+      </c>
+      <c r="R12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6436,6 +6472,9 @@
         <v>5</v>
       </c>
       <c r="Q13" s="2">
+        <v>17</v>
+      </c>
+      <c r="R13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6489,6 +6528,9 @@
         <v>4</v>
       </c>
       <c r="Q14" s="2">
+        <v>-14</v>
+      </c>
+      <c r="R14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6542,6 +6584,9 @@
         <v>-22</v>
       </c>
       <c r="Q15" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6595,6 +6640,9 @@
         <v>5</v>
       </c>
       <c r="Q16" s="2">
+        <v>12</v>
+      </c>
+      <c r="R16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6648,6 +6696,9 @@
         <v>3</v>
       </c>
       <c r="Q17" s="2">
+        <v>6</v>
+      </c>
+      <c r="R17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6701,6 +6752,9 @@
         <v>2</v>
       </c>
       <c r="Q18" s="2">
+        <v>15</v>
+      </c>
+      <c r="R18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6754,6 +6808,9 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6807,6 +6864,9 @@
         <v>4</v>
       </c>
       <c r="Q20" s="2">
+        <v>-15</v>
+      </c>
+      <c r="R20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6860,6 +6920,9 @@
         <v>13</v>
       </c>
       <c r="Q21" s="2">
+        <v>-18</v>
+      </c>
+      <c r="R21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6913,6 +6976,9 @@
         <v>1</v>
       </c>
       <c r="Q22" s="2">
+        <v>6</v>
+      </c>
+      <c r="R22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6966,6 +7032,9 @@
         <v>-18</v>
       </c>
       <c r="Q23" s="2">
+        <v>11</v>
+      </c>
+      <c r="R23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7062,10 +7131,13 @@
         <v>13</v>
       </c>
       <c r="O1" s="3">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3">
         <v>15</v>
       </c>
-      <c r="P1" s="3">
-        <v>14</v>
+      <c r="Q1" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7115,6 +7187,9 @@
         <v>44</v>
       </c>
       <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7165,6 +7240,9 @@
         <v>18</v>
       </c>
       <c r="P3" s="2">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7215,6 +7293,9 @@
         <v>59</v>
       </c>
       <c r="P4" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7265,6 +7346,9 @@
         <v>87</v>
       </c>
       <c r="P5" s="2">
+        <v>88</v>
+      </c>
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7315,6 +7399,9 @@
         <v>-11</v>
       </c>
       <c r="P6" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7365,6 +7452,9 @@
         <v>11</v>
       </c>
       <c r="P7" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7415,6 +7505,9 @@
         <v>13</v>
       </c>
       <c r="P8" s="2">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7465,6 +7558,9 @@
         <v>10</v>
       </c>
       <c r="P9" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7515,6 +7611,9 @@
         <v>-17</v>
       </c>
       <c r="P10" s="2">
+        <v>-35</v>
+      </c>
+      <c r="Q10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7565,6 +7664,9 @@
         <v>24</v>
       </c>
       <c r="P11" s="2">
+        <v>-18</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7615,6 +7717,9 @@
         <v>-16</v>
       </c>
       <c r="P12" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7682,6 +7787,9 @@
       <c r="Q1" s="3">
         <v>15</v>
       </c>
+      <c r="R1" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -7735,6 +7843,9 @@
       <c r="Q2" s="1">
         <v>27</v>
       </c>
+      <c r="R2" s="1">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -7788,6 +7899,9 @@
       <c r="Q3" s="1">
         <v>24.1</v>
       </c>
+      <c r="R3" s="1">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
@@ -7841,6 +7955,9 @@
       <c r="Q4" s="1">
         <v>27.8</v>
       </c>
+      <c r="R4" s="1">
+        <v>28.1</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -7894,6 +8011,9 @@
       <c r="Q5" s="1">
         <v>26.6</v>
       </c>
+      <c r="R5" s="1">
+        <v>26.9</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
@@ -7947,6 +8067,9 @@
       <c r="Q6" s="1">
         <v>27.3</v>
       </c>
+      <c r="R6" s="1">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
@@ -7992,6 +8115,9 @@
       <c r="Q7" s="1">
         <v>14.5</v>
       </c>
+      <c r="R7" s="1">
+        <v>15.1</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
@@ -8045,6 +8171,9 @@
       <c r="Q8" s="1">
         <v>24.9</v>
       </c>
+      <c r="R8" s="1">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -8098,6 +8227,9 @@
       <c r="Q9" s="1">
         <v>24</v>
       </c>
+      <c r="R9" s="1">
+        <v>23.7</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
@@ -8151,6 +8283,9 @@
       <c r="Q10" s="1">
         <v>6.4</v>
       </c>
+      <c r="R10" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
@@ -8204,6 +8339,9 @@
       <c r="Q11" s="1">
         <v>9</v>
       </c>
+      <c r="R11" s="1">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -8249,6 +8387,9 @@
       <c r="Q12" s="1">
         <v>9.7</v>
       </c>
+      <c r="R12" s="1">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
@@ -8302,6 +8443,9 @@
       <c r="Q13" s="1">
         <v>8.2</v>
       </c>
+      <c r="R13" s="1">
+        <v>8.8</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
@@ -8355,6 +8499,9 @@
       <c r="Q14" s="1">
         <v>6.8</v>
       </c>
+      <c r="R14" s="1">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
@@ -8408,6 +8555,9 @@
       <c r="Q15" s="1">
         <v>3</v>
       </c>
+      <c r="R15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
@@ -8461,6 +8611,9 @@
       <c r="Q16" s="1">
         <v>8.9</v>
       </c>
+      <c r="R16" s="1">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
@@ -8514,6 +8667,9 @@
       <c r="Q17" s="1">
         <v>5.8</v>
       </c>
+      <c r="R17" s="1">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
@@ -8567,6 +8723,9 @@
       <c r="Q18" s="1">
         <v>4.8</v>
       </c>
+      <c r="R18" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
@@ -8620,6 +8779,9 @@
       <c r="Q19" s="1">
         <v>8.4</v>
       </c>
+      <c r="R19" s="1">
+        <v>8.2</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
@@ -8673,6 +8835,9 @@
       <c r="Q20" s="1">
         <v>12</v>
       </c>
+      <c r="R20" s="1">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
@@ -8726,6 +8891,9 @@
       <c r="Q21" s="1">
         <v>10.6</v>
       </c>
+      <c r="R21" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
@@ -8779,6 +8947,9 @@
       <c r="Q22" s="1">
         <v>3</v>
       </c>
+      <c r="R22" s="1">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
@@ -8830,6 +9001,9 @@
         <v>3</v>
       </c>
       <c r="Q23" s="1">
+        <v>3</v>
+      </c>
+      <c r="R23" s="1">
         <v>3</v>
       </c>
     </row>
@@ -8929,6 +9103,9 @@
       <c r="P1" s="3">
         <v>15</v>
       </c>
+      <c r="Q1" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -8979,6 +9156,9 @@
       <c r="P2" s="1">
         <v>31.9</v>
       </c>
+      <c r="Q2" s="1">
+        <v>32.2</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
@@ -9029,6 +9209,9 @@
       <c r="P3" s="1">
         <v>27.5</v>
       </c>
+      <c r="Q3" s="1">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
@@ -9079,6 +9262,9 @@
       <c r="P4" s="1">
         <v>31.8</v>
       </c>
+      <c r="Q4" s="1">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -9129,6 +9315,9 @@
       <c r="P5" s="1">
         <v>33.5</v>
       </c>
+      <c r="Q5" s="1">
+        <v>33.8</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
@@ -9179,6 +9368,9 @@
       <c r="P6" s="1">
         <v>14</v>
       </c>
+      <c r="Q6" s="1">
+        <v>13.8</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
@@ -9229,6 +9421,9 @@
       <c r="P7" s="1">
         <v>14.7</v>
       </c>
+      <c r="Q7" s="1">
+        <v>15.3</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
@@ -9279,6 +9474,9 @@
       <c r="P8" s="1">
         <v>10.2</v>
       </c>
+      <c r="Q8" s="1">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
@@ -9329,6 +9527,9 @@
       <c r="P9" s="1">
         <v>6.3</v>
       </c>
+      <c r="Q9" s="1">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
@@ -9379,6 +9580,9 @@
       <c r="P10" s="1">
         <v>19.5</v>
       </c>
+      <c r="Q10" s="1">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
@@ -9429,6 +9633,9 @@
       <c r="P11" s="1">
         <v>8.6</v>
       </c>
+      <c r="Q11" s="1">
+        <v>9.2</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
@@ -9478,6 +9685,9 @@
       </c>
       <c r="P12" s="1">
         <v>3</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/f1_fantasy_archive.xlsx
+++ b/data/f1_fantasy_archive.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98229F0-2B07-4F07-A68F-AC4F3D4F854E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="13" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
+    <workbookView activeTab="15" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Drivers Points" sheetId="1" r:id="rId1"/>
@@ -5817,6 +5817,9 @@
       <c r="R1" s="3">
         <v>16</v>
       </c>
+      <c r="S1" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -5871,6 +5874,9 @@
         <v>-11</v>
       </c>
       <c r="R2" s="2">
+        <v>16</v>
+      </c>
+      <c r="S2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5927,6 +5933,9 @@
         <v>0</v>
       </c>
       <c r="R3" s="2">
+        <v>29</v>
+      </c>
+      <c r="S3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5983,6 +5992,9 @@
         <v>45</v>
       </c>
       <c r="R4" s="2">
+        <v>-5</v>
+      </c>
+      <c r="S4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6039,6 +6051,9 @@
         <v>28</v>
       </c>
       <c r="R5" s="2">
+        <v>29</v>
+      </c>
+      <c r="S5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6095,6 +6110,9 @@
         <v>43</v>
       </c>
       <c r="R6" s="2">
+        <v>57</v>
+      </c>
+      <c r="S6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6145,6 +6163,9 @@
         <v>26</v>
       </c>
       <c r="R7" s="2">
+        <v>25</v>
+      </c>
+      <c r="S7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6201,6 +6222,9 @@
         <v>15</v>
       </c>
       <c r="R8" s="2">
+        <v>32</v>
+      </c>
+      <c r="S8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6257,6 +6281,9 @@
         <v>20</v>
       </c>
       <c r="R9" s="2">
+        <v>33</v>
+      </c>
+      <c r="S9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6313,6 +6340,9 @@
         <v>-16</v>
       </c>
       <c r="R10" s="2">
+        <v>-10</v>
+      </c>
+      <c r="S10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6369,6 +6399,9 @@
         <v>15</v>
       </c>
       <c r="R11" s="2">
+        <v>4</v>
+      </c>
+      <c r="S11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6419,6 +6452,9 @@
         <v>3</v>
       </c>
       <c r="R12" s="2">
+        <v>17</v>
+      </c>
+      <c r="S12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6475,6 +6511,9 @@
         <v>17</v>
       </c>
       <c r="R13" s="2">
+        <v>28</v>
+      </c>
+      <c r="S13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6531,6 +6570,9 @@
         <v>-14</v>
       </c>
       <c r="R14" s="2">
+        <v>17</v>
+      </c>
+      <c r="S14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6587,6 +6629,9 @@
         <v>-20</v>
       </c>
       <c r="R15" s="2">
+        <v>11</v>
+      </c>
+      <c r="S15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6643,6 +6688,9 @@
         <v>12</v>
       </c>
       <c r="R16" s="2">
+        <v>12</v>
+      </c>
+      <c r="S16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6699,6 +6747,9 @@
         <v>6</v>
       </c>
       <c r="R17" s="2">
+        <v>7</v>
+      </c>
+      <c r="S17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6755,6 +6806,9 @@
         <v>15</v>
       </c>
       <c r="R18" s="2">
+        <v>19</v>
+      </c>
+      <c r="S18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6811,6 +6865,9 @@
         <v>8</v>
       </c>
       <c r="R19" s="2">
+        <v>4</v>
+      </c>
+      <c r="S19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6869,6 +6926,9 @@
       <c r="R20" s="2">
         <v>0</v>
       </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
@@ -6923,6 +6983,9 @@
         <v>-18</v>
       </c>
       <c r="R21" s="2">
+        <v>13</v>
+      </c>
+      <c r="S21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6979,6 +7042,9 @@
         <v>6</v>
       </c>
       <c r="R22" s="2">
+        <v>-20</v>
+      </c>
+      <c r="S22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7035,6 +7101,9 @@
         <v>11</v>
       </c>
       <c r="R23" s="2">
+        <v>9</v>
+      </c>
+      <c r="S23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7139,6 +7208,9 @@
       <c r="Q1" s="3">
         <v>16</v>
       </c>
+      <c r="R1" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -7190,6 +7262,9 @@
         <v>1</v>
       </c>
       <c r="Q2" s="2">
+        <v>57</v>
+      </c>
+      <c r="R2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7243,6 +7318,9 @@
         <v>45</v>
       </c>
       <c r="Q3" s="2">
+        <v>80</v>
+      </c>
+      <c r="R3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7296,6 +7374,9 @@
         <v>71</v>
       </c>
       <c r="Q4" s="2">
+        <v>97</v>
+      </c>
+      <c r="R4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7349,6 +7430,9 @@
         <v>88</v>
       </c>
       <c r="Q5" s="2">
+        <v>39</v>
+      </c>
+      <c r="R5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7402,6 +7486,9 @@
         <v>6</v>
       </c>
       <c r="Q6" s="2">
+        <v>5</v>
+      </c>
+      <c r="R6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7455,6 +7542,9 @@
         <v>21</v>
       </c>
       <c r="Q7" s="2">
+        <v>20</v>
+      </c>
+      <c r="R7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7508,6 +7598,9 @@
         <v>23</v>
       </c>
       <c r="Q8" s="2">
+        <v>53</v>
+      </c>
+      <c r="R8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7561,6 +7654,9 @@
         <v>27</v>
       </c>
       <c r="Q9" s="2">
+        <v>38</v>
+      </c>
+      <c r="R9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7614,6 +7710,9 @@
         <v>-35</v>
       </c>
       <c r="Q10" s="2">
+        <v>36</v>
+      </c>
+      <c r="R10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7667,6 +7766,9 @@
         <v>-18</v>
       </c>
       <c r="Q11" s="2">
+        <v>28</v>
+      </c>
+      <c r="R11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7720,6 +7822,9 @@
         <v>16</v>
       </c>
       <c r="Q12" s="2">
+        <v>-12</v>
+      </c>
+      <c r="R12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7790,6 +7895,9 @@
       <c r="R1" s="3">
         <v>16</v>
       </c>
+      <c r="S1" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -7846,6 +7954,9 @@
       <c r="R2" s="1">
         <v>26.7</v>
       </c>
+      <c r="S2" s="1">
+        <v>26.4</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -7902,6 +8013,9 @@
       <c r="R3" s="1">
         <v>24</v>
       </c>
+      <c r="S3" s="1">
+        <v>23.7</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
@@ -7958,6 +8072,9 @@
       <c r="R4" s="1">
         <v>28.1</v>
       </c>
+      <c r="S4" s="1">
+        <v>28</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -8014,6 +8131,9 @@
       <c r="R5" s="1">
         <v>26.9</v>
       </c>
+      <c r="S5" s="1">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
@@ -8070,6 +8190,9 @@
       <c r="R6" s="1">
         <v>27.6</v>
       </c>
+      <c r="S6" s="1">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
@@ -8118,6 +8241,9 @@
       <c r="R7" s="1">
         <v>15.1</v>
       </c>
+      <c r="S7" s="1">
+        <v>15.7</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
@@ -8174,6 +8300,9 @@
       <c r="R8" s="1">
         <v>24.6</v>
       </c>
+      <c r="S8" s="1">
+        <v>24.3</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -8230,6 +8359,9 @@
       <c r="R9" s="1">
         <v>23.7</v>
       </c>
+      <c r="S9" s="1">
+        <v>23.8</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
@@ -8286,6 +8418,9 @@
       <c r="R10" s="1">
         <v>5.8</v>
       </c>
+      <c r="S10" s="1">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
@@ -8342,6 +8477,9 @@
       <c r="R11" s="1">
         <v>8.4</v>
       </c>
+      <c r="S11" s="1">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -8390,6 +8528,9 @@
       <c r="R12" s="1">
         <v>9.1</v>
       </c>
+      <c r="S12" s="1">
+        <v>9.3</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
@@ -8446,6 +8587,9 @@
       <c r="R13" s="1">
         <v>8.8</v>
       </c>
+      <c r="S13" s="1">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
@@ -8502,6 +8646,9 @@
       <c r="R14" s="1">
         <v>6.2</v>
       </c>
+      <c r="S14" s="1">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
@@ -8558,6 +8705,9 @@
       <c r="R15" s="1">
         <v>3</v>
       </c>
+      <c r="S15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
@@ -8614,6 +8764,9 @@
       <c r="R16" s="1">
         <v>9.1</v>
       </c>
+      <c r="S16" s="1">
+        <v>9.3</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
@@ -8670,6 +8823,9 @@
       <c r="R17" s="1">
         <v>5.6</v>
       </c>
+      <c r="S17" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
@@ -8726,6 +8882,9 @@
       <c r="R18" s="1">
         <v>5.4</v>
       </c>
+      <c r="S18" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
@@ -8782,6 +8941,9 @@
       <c r="R19" s="1">
         <v>8.2</v>
       </c>
+      <c r="S19" s="1">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
@@ -8838,6 +9000,9 @@
       <c r="R20" s="1">
         <v>11.4</v>
       </c>
+      <c r="S20" s="1">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
@@ -8894,6 +9059,9 @@
       <c r="R21" s="1">
         <v>10</v>
       </c>
+      <c r="S21" s="1">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
@@ -8950,6 +9118,9 @@
       <c r="R22" s="1">
         <v>3.6</v>
       </c>
+      <c r="S22" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
@@ -9004,6 +9175,9 @@
         <v>3</v>
       </c>
       <c r="R23" s="1">
+        <v>3</v>
+      </c>
+      <c r="S23" s="1">
         <v>3</v>
       </c>
     </row>
@@ -9106,6 +9280,9 @@
       <c r="Q1" s="3">
         <v>16</v>
       </c>
+      <c r="R1" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -9159,6 +9336,9 @@
       <c r="Q2" s="1">
         <v>32.2</v>
       </c>
+      <c r="R2" s="1">
+        <v>32.3</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
@@ -9212,6 +9392,9 @@
       <c r="Q3" s="1">
         <v>27.6</v>
       </c>
+      <c r="R3" s="1">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
@@ -9265,6 +9448,9 @@
       <c r="Q4" s="1">
         <v>32.1</v>
       </c>
+      <c r="R4" s="1">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -9318,6 +9504,9 @@
       <c r="Q5" s="1">
         <v>33.8</v>
       </c>
+      <c r="R5" s="1">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
@@ -9371,6 +9560,9 @@
       <c r="Q6" s="1">
         <v>13.8</v>
       </c>
+      <c r="R6" s="1">
+        <v>13.2</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
@@ -9424,6 +9616,9 @@
       <c r="Q7" s="1">
         <v>15.3</v>
       </c>
+      <c r="R7" s="1">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
@@ -9477,6 +9672,9 @@
       <c r="Q8" s="1">
         <v>10.8</v>
       </c>
+      <c r="R8" s="1">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
@@ -9530,6 +9728,9 @@
       <c r="Q9" s="1">
         <v>5.7</v>
       </c>
+      <c r="R9" s="1">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
@@ -9583,6 +9784,9 @@
       <c r="Q10" s="1">
         <v>19.4</v>
       </c>
+      <c r="R10" s="1">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
@@ -9636,6 +9840,9 @@
       <c r="Q11" s="1">
         <v>9.2</v>
       </c>
+      <c r="R11" s="1">
+        <v>9.8</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
@@ -9688,6 +9895,9 @@
       </c>
       <c r="Q12" s="1">
         <v>3.6</v>
+      </c>
+      <c r="R12" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/f1_fantasy_archive.xlsx
+++ b/data/f1_fantasy_archive.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98229F0-2B07-4F07-A68F-AC4F3D4F854E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="15" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
+    <workbookView activeTab="13" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Drivers Points" sheetId="1" r:id="rId1"/>
@@ -5820,6 +5820,9 @@
       <c r="S1" s="3">
         <v>17</v>
       </c>
+      <c r="T1" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -5877,6 +5880,9 @@
         <v>16</v>
       </c>
       <c r="S2" s="2">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5936,6 +5942,9 @@
         <v>29</v>
       </c>
       <c r="S3" s="2">
+        <v>6</v>
+      </c>
+      <c r="T3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5995,6 +6004,9 @@
         <v>-5</v>
       </c>
       <c r="S4" s="2">
+        <v>17</v>
+      </c>
+      <c r="T4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6054,6 +6066,9 @@
         <v>29</v>
       </c>
       <c r="S5" s="2">
+        <v>33</v>
+      </c>
+      <c r="T5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6113,6 +6128,9 @@
         <v>57</v>
       </c>
       <c r="S6" s="2">
+        <v>53</v>
+      </c>
+      <c r="T6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6166,6 +6184,9 @@
         <v>25</v>
       </c>
       <c r="S7" s="2">
+        <v>8</v>
+      </c>
+      <c r="T7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6225,6 +6246,9 @@
         <v>32</v>
       </c>
       <c r="S8" s="2">
+        <v>33</v>
+      </c>
+      <c r="T8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6284,6 +6308,9 @@
         <v>33</v>
       </c>
       <c r="S9" s="2">
+        <v>43</v>
+      </c>
+      <c r="T9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6343,6 +6370,9 @@
         <v>-10</v>
       </c>
       <c r="S10" s="2">
+        <v>-10</v>
+      </c>
+      <c r="T10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6402,6 +6432,9 @@
         <v>4</v>
       </c>
       <c r="S11" s="2">
+        <v>13</v>
+      </c>
+      <c r="T11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6455,6 +6488,9 @@
         <v>17</v>
       </c>
       <c r="S12" s="2">
+        <v>18</v>
+      </c>
+      <c r="T12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6514,6 +6550,9 @@
         <v>28</v>
       </c>
       <c r="S13" s="2">
+        <v>1</v>
+      </c>
+      <c r="T13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6573,6 +6612,9 @@
         <v>17</v>
       </c>
       <c r="S14" s="2">
+        <v>11</v>
+      </c>
+      <c r="T14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6632,6 +6674,9 @@
         <v>11</v>
       </c>
       <c r="S15" s="2">
+        <v>-28</v>
+      </c>
+      <c r="T15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6691,6 +6736,9 @@
         <v>12</v>
       </c>
       <c r="S16" s="2">
+        <v>12</v>
+      </c>
+      <c r="T16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6750,6 +6798,9 @@
         <v>7</v>
       </c>
       <c r="S17" s="2">
+        <v>18</v>
+      </c>
+      <c r="T17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6809,6 +6860,9 @@
         <v>19</v>
       </c>
       <c r="S18" s="2">
+        <v>17</v>
+      </c>
+      <c r="T18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6868,6 +6922,9 @@
         <v>4</v>
       </c>
       <c r="S19" s="2">
+        <v>-29</v>
+      </c>
+      <c r="T19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6927,6 +6984,9 @@
         <v>0</v>
       </c>
       <c r="S20" s="2">
+        <v>3</v>
+      </c>
+      <c r="T20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6986,6 +7046,9 @@
         <v>13</v>
       </c>
       <c r="S21" s="2">
+        <v>-28</v>
+      </c>
+      <c r="T21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7045,6 +7108,9 @@
         <v>-20</v>
       </c>
       <c r="S22" s="2">
+        <v>-11</v>
+      </c>
+      <c r="T22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7104,6 +7170,9 @@
         <v>9</v>
       </c>
       <c r="S23" s="2">
+        <v>-9</v>
+      </c>
+      <c r="T23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7211,6 +7280,9 @@
       <c r="R1" s="3">
         <v>17</v>
       </c>
+      <c r="S1" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -7265,6 +7337,9 @@
         <v>57</v>
       </c>
       <c r="R2" s="2">
+        <v>36</v>
+      </c>
+      <c r="S2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7321,6 +7396,9 @@
         <v>80</v>
       </c>
       <c r="R3" s="2">
+        <v>91</v>
+      </c>
+      <c r="S3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7377,6 +7455,9 @@
         <v>97</v>
       </c>
       <c r="R4" s="2">
+        <v>66</v>
+      </c>
+      <c r="S4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7433,6 +7514,9 @@
         <v>39</v>
       </c>
       <c r="R5" s="2">
+        <v>65</v>
+      </c>
+      <c r="S5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7489,6 +7573,9 @@
         <v>5</v>
       </c>
       <c r="R6" s="2">
+        <v>6</v>
+      </c>
+      <c r="S6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7545,6 +7632,9 @@
         <v>20</v>
       </c>
       <c r="R7" s="2">
+        <v>35</v>
+      </c>
+      <c r="S7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7601,6 +7691,9 @@
         <v>53</v>
       </c>
       <c r="R8" s="2">
+        <v>34</v>
+      </c>
+      <c r="S8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7657,6 +7750,9 @@
         <v>38</v>
       </c>
       <c r="R9" s="2">
+        <v>-9</v>
+      </c>
+      <c r="S9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7713,6 +7809,9 @@
         <v>36</v>
       </c>
       <c r="R10" s="2">
+        <v>-13</v>
+      </c>
+      <c r="S10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7769,6 +7868,9 @@
         <v>28</v>
       </c>
       <c r="R11" s="2">
+        <v>-20</v>
+      </c>
+      <c r="S11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7825,6 +7927,9 @@
         <v>-12</v>
       </c>
       <c r="R12" s="2">
+        <v>-21</v>
+      </c>
+      <c r="S12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7898,6 +8003,9 @@
       <c r="S1" s="3">
         <v>17</v>
       </c>
+      <c r="T1" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -7957,6 +8065,9 @@
       <c r="S2" s="1">
         <v>26.4</v>
       </c>
+      <c r="T2" s="1">
+        <v>26.1</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -8016,6 +8127,9 @@
       <c r="S3" s="1">
         <v>23.7</v>
       </c>
+      <c r="T3" s="1">
+        <v>23.4</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
@@ -8075,6 +8189,9 @@
       <c r="S4" s="1">
         <v>28</v>
       </c>
+      <c r="T4" s="1">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -8134,6 +8251,9 @@
       <c r="S5" s="1">
         <v>27</v>
       </c>
+      <c r="T5" s="1">
+        <v>27.1</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
@@ -8193,6 +8313,9 @@
       <c r="S6" s="1">
         <v>27.9</v>
       </c>
+      <c r="T6" s="1">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
@@ -8244,6 +8367,9 @@
       <c r="S7" s="1">
         <v>15.7</v>
       </c>
+      <c r="T7" s="1">
+        <v>16.3</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
@@ -8303,6 +8429,9 @@
       <c r="S8" s="1">
         <v>24.3</v>
       </c>
+      <c r="T8" s="1">
+        <v>24.4</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -8362,6 +8491,9 @@
       <c r="S9" s="1">
         <v>23.8</v>
       </c>
+      <c r="T9" s="1">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
@@ -8421,6 +8553,9 @@
       <c r="S10" s="1">
         <v>5.2</v>
       </c>
+      <c r="T10" s="1">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
@@ -8480,6 +8615,9 @@
       <c r="S11" s="1">
         <v>7.8</v>
       </c>
+      <c r="T11" s="1">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -8531,6 +8669,9 @@
       <c r="S12" s="1">
         <v>9.3</v>
       </c>
+      <c r="T12" s="1">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
@@ -8590,6 +8731,9 @@
       <c r="S13" s="1">
         <v>9.4</v>
       </c>
+      <c r="T13" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
@@ -8649,6 +8793,9 @@
       <c r="S14" s="1">
         <v>5.6</v>
       </c>
+      <c r="T14" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
@@ -8708,6 +8855,9 @@
       <c r="S15" s="1">
         <v>3</v>
       </c>
+      <c r="T15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
@@ -8767,6 +8917,9 @@
       <c r="S16" s="1">
         <v>9.3</v>
       </c>
+      <c r="T16" s="1">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
@@ -8826,6 +8979,9 @@
       <c r="S17" s="1">
         <v>5.8</v>
       </c>
+      <c r="T17" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
@@ -8885,6 +9041,9 @@
       <c r="S18" s="1">
         <v>6</v>
       </c>
+      <c r="T18" s="1">
+        <v>6.6</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
@@ -8944,6 +9103,9 @@
       <c r="S19" s="1">
         <v>7.6</v>
       </c>
+      <c r="T19" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
@@ -9003,6 +9165,9 @@
       <c r="S20" s="1">
         <v>10.8</v>
       </c>
+      <c r="T20" s="1">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
@@ -9062,6 +9227,9 @@
       <c r="S21" s="1">
         <v>9.4</v>
       </c>
+      <c r="T21" s="1">
+        <v>8.8</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
@@ -9121,6 +9289,9 @@
       <c r="S22" s="1">
         <v>3</v>
       </c>
+      <c r="T22" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
@@ -9179,6 +9350,9 @@
       </c>
       <c r="S23" s="1">
         <v>3</v>
+      </c>
+      <c r="T23" s="1">
+        <v>3.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9283,6 +9457,9 @@
       <c r="R1" s="3">
         <v>17</v>
       </c>
+      <c r="S1" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -9339,6 +9516,9 @@
       <c r="R2" s="1">
         <v>32.3</v>
       </c>
+      <c r="S2" s="1">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
@@ -9395,6 +9575,9 @@
       <c r="R3" s="1">
         <v>27.9</v>
       </c>
+      <c r="S3" s="1">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
@@ -9451,6 +9634,9 @@
       <c r="R4" s="1">
         <v>32.4</v>
       </c>
+      <c r="S4" s="1">
+        <v>32.7</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -9507,6 +9693,9 @@
       <c r="R5" s="1">
         <v>34</v>
       </c>
+      <c r="S5" s="1">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
@@ -9563,6 +9752,9 @@
       <c r="R6" s="1">
         <v>13.2</v>
       </c>
+      <c r="S6" s="1">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
@@ -9619,6 +9811,9 @@
       <c r="R7" s="1">
         <v>15.9</v>
       </c>
+      <c r="S7" s="1">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
@@ -9675,6 +9870,9 @@
       <c r="R8" s="1">
         <v>11.4</v>
       </c>
+      <c r="S8" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
@@ -9731,6 +9929,9 @@
       <c r="R9" s="1">
         <v>5.1</v>
       </c>
+      <c r="S9" s="1">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
@@ -9787,6 +9988,9 @@
       <c r="R10" s="1">
         <v>19.1</v>
       </c>
+      <c r="S10" s="1">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
@@ -9843,6 +10047,9 @@
       <c r="R11" s="1">
         <v>9.8</v>
       </c>
+      <c r="S11" s="1">
+        <v>10.4</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
@@ -9897,6 +10104,9 @@
         <v>3.6</v>
       </c>
       <c r="R12" s="1">
+        <v>3</v>
+      </c>
+      <c r="S12" s="1">
         <v>3</v>
       </c>
     </row>

--- a/data/f1_fantasy_archive.xlsx
+++ b/data/f1_fantasy_archive.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98229F0-2B07-4F07-A68F-AC4F3D4F854E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="13" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
+    <workbookView activeTab="14" firstSheet="10" windowHeight="15840" windowWidth="29040" xWindow="-120" xr2:uid="{5075C4C2-DC0E-48A5-BDF1-482703F248E6}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Drivers Points" sheetId="1" r:id="rId1"/>
@@ -5823,6 +5823,9 @@
       <c r="T1" s="3">
         <v>18</v>
       </c>
+      <c r="U1" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -5883,6 +5886,9 @@
         <v>18</v>
       </c>
       <c r="T2" s="2">
+        <v>18</v>
+      </c>
+      <c r="U2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5945,6 +5951,9 @@
         <v>6</v>
       </c>
       <c r="T3" s="2">
+        <v>15</v>
+      </c>
+      <c r="U3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6007,6 +6016,9 @@
         <v>17</v>
       </c>
       <c r="T4" s="2">
+        <v>9</v>
+      </c>
+      <c r="U4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6069,6 +6081,9 @@
         <v>33</v>
       </c>
       <c r="T5" s="2">
+        <v>36</v>
+      </c>
+      <c r="U5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6131,6 +6146,9 @@
         <v>53</v>
       </c>
       <c r="T6" s="2">
+        <v>27</v>
+      </c>
+      <c r="U6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6187,6 +6205,9 @@
         <v>8</v>
       </c>
       <c r="T7" s="2">
+        <v>13</v>
+      </c>
+      <c r="U7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6249,6 +6270,9 @@
         <v>33</v>
       </c>
       <c r="T8" s="2">
+        <v>23</v>
+      </c>
+      <c r="U8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6311,6 +6335,9 @@
         <v>43</v>
       </c>
       <c r="T9" s="2">
+        <v>53</v>
+      </c>
+      <c r="U9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6373,6 +6400,9 @@
         <v>-10</v>
       </c>
       <c r="T10" s="2">
+        <v>7</v>
+      </c>
+      <c r="U10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6435,6 +6465,9 @@
         <v>13</v>
       </c>
       <c r="T11" s="2">
+        <v>3</v>
+      </c>
+      <c r="U11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6491,6 +6524,9 @@
         <v>18</v>
       </c>
       <c r="T12" s="2">
+        <v>5</v>
+      </c>
+      <c r="U12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6553,6 +6589,9 @@
         <v>1</v>
       </c>
       <c r="T13" s="2">
+        <v>11</v>
+      </c>
+      <c r="U13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6615,6 +6654,9 @@
         <v>11</v>
       </c>
       <c r="T14" s="2">
+        <v>2</v>
+      </c>
+      <c r="U14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6677,6 +6719,9 @@
         <v>-28</v>
       </c>
       <c r="T15" s="2">
+        <v>12</v>
+      </c>
+      <c r="U15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6739,6 +6784,9 @@
         <v>12</v>
       </c>
       <c r="T16" s="2">
+        <v>7</v>
+      </c>
+      <c r="U16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6801,6 +6849,9 @@
         <v>18</v>
       </c>
       <c r="T17" s="2">
+        <v>-13</v>
+      </c>
+      <c r="U17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6863,6 +6914,9 @@
         <v>17</v>
       </c>
       <c r="T18" s="2">
+        <v>7</v>
+      </c>
+      <c r="U18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6925,6 +6979,9 @@
         <v>-29</v>
       </c>
       <c r="T19" s="2">
+        <v>17</v>
+      </c>
+      <c r="U19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6987,6 +7044,9 @@
         <v>3</v>
       </c>
       <c r="T20" s="2">
+        <v>3</v>
+      </c>
+      <c r="U20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7049,6 +7109,9 @@
         <v>-28</v>
       </c>
       <c r="T21" s="2">
+        <v>-18</v>
+      </c>
+      <c r="U21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7111,6 +7174,9 @@
         <v>-11</v>
       </c>
       <c r="T22" s="2">
+        <v>-19</v>
+      </c>
+      <c r="U22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7173,6 +7239,9 @@
         <v>-9</v>
       </c>
       <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7283,6 +7352,9 @@
       <c r="S1" s="3">
         <v>18</v>
       </c>
+      <c r="T1" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -7340,6 +7412,9 @@
         <v>36</v>
       </c>
       <c r="S2" s="2">
+        <v>58</v>
+      </c>
+      <c r="T2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7399,6 +7474,9 @@
         <v>91</v>
       </c>
       <c r="S3" s="2">
+        <v>81</v>
+      </c>
+      <c r="T3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7458,6 +7536,9 @@
         <v>66</v>
       </c>
       <c r="S4" s="2">
+        <v>55</v>
+      </c>
+      <c r="T4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7517,6 +7598,9 @@
         <v>65</v>
       </c>
       <c r="S5" s="2">
+        <v>57</v>
+      </c>
+      <c r="T5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7576,6 +7660,9 @@
         <v>6</v>
       </c>
       <c r="S6" s="2">
+        <v>11</v>
+      </c>
+      <c r="T6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7635,6 +7722,9 @@
         <v>35</v>
       </c>
       <c r="S7" s="2">
+        <v>-3</v>
+      </c>
+      <c r="T7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7694,6 +7784,9 @@
         <v>34</v>
       </c>
       <c r="S8" s="2">
+        <v>31</v>
+      </c>
+      <c r="T8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7753,6 +7846,9 @@
         <v>-9</v>
       </c>
       <c r="S9" s="2">
+        <v>29</v>
+      </c>
+      <c r="T9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7812,6 +7908,9 @@
         <v>-13</v>
       </c>
       <c r="S10" s="2">
+        <v>17</v>
+      </c>
+      <c r="T10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7871,6 +7970,9 @@
         <v>-20</v>
       </c>
       <c r="S11" s="2">
+        <v>-12</v>
+      </c>
+      <c r="T11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7930,6 +8032,9 @@
         <v>-21</v>
       </c>
       <c r="S12" s="2">
+        <v>-18</v>
+      </c>
+      <c r="T12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8006,6 +8111,9 @@
       <c r="T1" s="3">
         <v>18</v>
       </c>
+      <c r="U1" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -8068,6 +8176,9 @@
       <c r="T2" s="1">
         <v>26.1</v>
       </c>
+      <c r="U2" s="1">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -8130,6 +8241,9 @@
       <c r="T3" s="1">
         <v>23.4</v>
       </c>
+      <c r="U3" s="1">
+        <v>23.3</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
@@ -8192,6 +8306,9 @@
       <c r="T4" s="1">
         <v>27.9</v>
       </c>
+      <c r="U4" s="1">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -8254,6 +8371,9 @@
       <c r="T5" s="1">
         <v>27.1</v>
       </c>
+      <c r="U5" s="1">
+        <v>27.4</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
@@ -8316,6 +8436,9 @@
       <c r="T6" s="1">
         <v>28.2</v>
       </c>
+      <c r="U6" s="1">
+        <v>28.5</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
@@ -8370,6 +8493,9 @@
       <c r="T7" s="1">
         <v>16.3</v>
       </c>
+      <c r="U7" s="1">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
@@ -8432,6 +8558,9 @@
       <c r="T8" s="1">
         <v>24.4</v>
       </c>
+      <c r="U8" s="1">
+        <v>24.7</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -8494,6 +8623,9 @@
       <c r="T9" s="1">
         <v>24.1</v>
       </c>
+      <c r="U9" s="1">
+        <v>24.4</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
@@ -8556,6 +8688,9 @@
       <c r="T10" s="1">
         <v>4.6</v>
       </c>
+      <c r="U10" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
@@ -8618,6 +8753,9 @@
       <c r="T11" s="1">
         <v>8.4</v>
       </c>
+      <c r="U11" s="1">
+        <v>8.2</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
@@ -8672,6 +8810,9 @@
       <c r="T12" s="1">
         <v>9.9</v>
       </c>
+      <c r="U12" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
@@ -8734,6 +8875,9 @@
       <c r="T13" s="1">
         <v>10</v>
       </c>
+      <c r="U13" s="1">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
@@ -8796,6 +8940,9 @@
       <c r="T14" s="1">
         <v>5.4</v>
       </c>
+      <c r="U14" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
@@ -8858,6 +9005,9 @@
       <c r="T15" s="1">
         <v>3</v>
       </c>
+      <c r="U15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
@@ -8920,6 +9070,9 @@
       <c r="T16" s="1">
         <v>9.9</v>
       </c>
+      <c r="U16" s="1">
+        <v>10.1</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
@@ -8982,6 +9135,9 @@
       <c r="T17" s="1">
         <v>6.4</v>
       </c>
+      <c r="U17" s="1">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
@@ -9044,6 +9200,9 @@
       <c r="T18" s="1">
         <v>6.6</v>
       </c>
+      <c r="U18" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
@@ -9106,6 +9265,9 @@
       <c r="T19" s="1">
         <v>7</v>
       </c>
+      <c r="U19" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
@@ -9168,6 +9330,9 @@
       <c r="T20" s="1">
         <v>10.2</v>
       </c>
+      <c r="U20" s="1">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
@@ -9230,6 +9395,9 @@
       <c r="T21" s="1">
         <v>8.8</v>
       </c>
+      <c r="U21" s="1">
+        <v>8.2</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
@@ -9292,6 +9460,9 @@
       <c r="T22" s="1">
         <v>3</v>
       </c>
+      <c r="U22" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
@@ -9353,6 +9524,9 @@
       </c>
       <c r="T23" s="1">
         <v>3.6</v>
+      </c>
+      <c r="U23" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9460,6 +9634,9 @@
       <c r="S1" s="3">
         <v>18</v>
       </c>
+      <c r="T1" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
@@ -9519,6 +9696,9 @@
       <c r="S2" s="1">
         <v>32.4</v>
       </c>
+      <c r="T2" s="1">
+        <v>32.7</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
@@ -9578,6 +9758,9 @@
       <c r="S3" s="1">
         <v>28.2</v>
       </c>
+      <c r="T3" s="1">
+        <v>28.5</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
@@ -9637,6 +9820,9 @@
       <c r="S4" s="1">
         <v>32.7</v>
       </c>
+      <c r="T4" s="1">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -9696,6 +9882,9 @@
       <c r="S5" s="1">
         <v>34</v>
       </c>
+      <c r="T5" s="1">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
@@ -9755,6 +9944,9 @@
       <c r="S6" s="1">
         <v>12.6</v>
       </c>
+      <c r="T6" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
@@ -9814,6 +10006,9 @@
       <c r="S7" s="1">
         <v>16.5</v>
       </c>
+      <c r="T7" s="1">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
@@ -9873,6 +10068,9 @@
       <c r="S8" s="1">
         <v>12</v>
       </c>
+      <c r="T8" s="1">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
@@ -9932,6 +10130,9 @@
       <c r="S9" s="1">
         <v>4.5</v>
       </c>
+      <c r="T9" s="1">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
@@ -9991,6 +10192,9 @@
       <c r="S10" s="1">
         <v>18.8</v>
       </c>
+      <c r="T10" s="1">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
@@ -10050,6 +10254,9 @@
       <c r="S11" s="1">
         <v>10.4</v>
       </c>
+      <c r="T11" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
@@ -10107,6 +10314,9 @@
         <v>3</v>
       </c>
       <c r="S12" s="1">
+        <v>3</v>
+      </c>
+      <c r="T12" s="1">
         <v>3</v>
       </c>
     </row>
